--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY180"/>
+  <dimension ref="A1:AY181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21643,6 +21643,126 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>122453583</v>
+      </c>
+      <c r="B181" t="n">
+        <v>56217</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Rödingträsket (AC2592), Ly lm</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>551999</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7266481</v>
+      </c>
+      <c r="S181" t="n">
+        <v>100</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>AC2592</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Darius Strasevicius</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Via Darius Strasevicius</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>Utter barmarksinventering RMÖ/GDP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -21648,7 +21648,7 @@
         <v>122453583</v>
       </c>
       <c r="B181" t="n">
-        <v>56217</v>
+        <v>56222</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -21663,11 +21663,6 @@
       <c r="E181" t="n">
         <v>100077</v>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>Lutra lutra</t>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -21648,7 +21648,7 @@
         <v>122453583</v>
       </c>
       <c r="B181" t="n">
-        <v>56222</v>
+        <v>56226</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21662,6 +21662,11 @@
       </c>
       <c r="E181" t="n">
         <v>100077</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -21648,7 +21648,7 @@
         <v>122453583</v>
       </c>
       <c r="B181" t="n">
-        <v>56226</v>
+        <v>56227</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -21648,7 +21648,7 @@
         <v>122453583</v>
       </c>
       <c r="B181" t="n">
-        <v>56227</v>
+        <v>56321</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>

--- a/artfynd/A 43891-2020 artfynd.xlsx
+++ b/artfynd/A 43891-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AY180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21643,126 +21643,6 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>122453583</v>
-      </c>
-      <c r="B181" t="n">
-        <v>56321</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>Rödingträsket (AC2592), Ly lm</t>
-        </is>
-      </c>
-      <c r="Q181" t="n">
-        <v>551999</v>
-      </c>
-      <c r="R181" t="n">
-        <v>7266481</v>
-      </c>
-      <c r="S181" t="n">
-        <v>100</v>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>AC2592</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AD181" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE181" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG181" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT181" t="inlineStr"/>
-      <c r="AW181" t="inlineStr">
-        <is>
-          <t>Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AX181" t="inlineStr">
-        <is>
-          <t>Via Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AY181" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
